--- a/calibration/CalibrationDatafile_prevax_Dhaka.xlsx
+++ b/calibration/CalibrationDatafile_prevax_Dhaka.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aliciakraay/PycharmProjects/rotasim/calibration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1E304B-41FD-3B49-960E-D8F4AACEED4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7AA67B-36C8-E34C-8C53-2BDD59F34B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5260" yWindow="4660" windowWidth="26040" windowHeight="14940" activeTab="2" xr2:uid="{C5260B54-9666-D54D-BEE2-B441C4FA991D}"/>
+    <workbookView xWindow="12040" yWindow="3540" windowWidth="26040" windowHeight="14940" xr2:uid="{C5260B54-9666-D54D-BEE2-B441C4FA991D}"/>
   </bookViews>
   <sheets>
     <sheet name="Dhaka_ageincidence" sheetId="1" r:id="rId1"/>
@@ -507,8 +507,8 @@
         <v>305106.46399999998</v>
       </c>
       <c r="E2">
-        <f>(C2/(D2*8))*100000</f>
-        <v>8.9722779521314902</v>
+        <f>(C2/(D2*7))*100000</f>
+        <v>10.254031945293132</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -526,8 +526,8 @@
         <v>305106.46399999998</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E5" si="0">(C3/(D3*8))*100000</f>
-        <v>6.718966137669244</v>
+        <f>(C3/(D3*7))*100000</f>
+        <v>7.6788184430505657</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -545,8 +545,8 @@
         <v>927054.25600000005</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>0.31012208631724353</v>
+        <f>(C4/(D4*7))*100000</f>
+        <v>0.35442524150542115</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -564,8 +564,8 @@
         <v>10197596.816</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>8.4578750813793707E-2</v>
+        <f>(C5/(D5*7))*100000</f>
+        <v>9.6661429501478505E-2</v>
       </c>
     </row>
   </sheetData>
